--- a/salidas/empresas/AFL.xlsx
+++ b/salidas/empresas/AFL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>14.48771858215332</v>
+        <v>14.48772144317627</v>
       </c>
       <c r="C2" t="n">
         <v>23.47500038146973</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>14.31085586547852</v>
+        <v>14.31084537506104</v>
       </c>
       <c r="C3" t="n">
         <v>23.125</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>13.96428871154785</v>
+        <v>13.9642972946167</v>
       </c>
       <c r="C4" t="n">
         <v>22.56500053405762</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>14.71001243591309</v>
+        <v>14.71000480651855</v>
       </c>
       <c r="C5" t="n">
         <v>23.77000045776367</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>14.51991558074951</v>
+        <v>14.51991844177246</v>
       </c>
       <c r="C6" t="n">
         <v>23.39999961853027</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>14.3803014755249</v>
+        <v>14.380295753479</v>
       </c>
       <c r="C7" t="n">
         <v>23.17499923706055</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>13.69463539123535</v>
+        <v>13.69463348388672</v>
       </c>
       <c r="C8" t="n">
         <v>22.06999969482422</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>14.02539730072021</v>
+        <v>14.02539825439453</v>
       </c>
       <c r="C9" t="n">
         <v>22.53499984741211</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.24012088775635</v>
+        <v>14.24011516571045</v>
       </c>
       <c r="C10" t="n">
         <v>22.8799991607666</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>13.97872066497803</v>
+        <v>13.97871971130371</v>
       </c>
       <c r="C11" t="n">
         <v>22.45999908447266</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>13.78550052642822</v>
+        <v>13.78549861907959</v>
       </c>
       <c r="C12" t="n">
         <v>22.06999969482422</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>14.86922550201416</v>
+        <v>14.86922836303711</v>
       </c>
       <c r="C14" t="n">
         <v>23.80500030517578</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>14.81094932556152</v>
+        <v>14.81094551086426</v>
       </c>
       <c r="C15" t="n">
         <v>23.6200008392334</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>14.75451850891113</v>
+        <v>14.75450611114502</v>
       </c>
       <c r="C16" t="n">
         <v>23.53000068664551</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>16.09639358520508</v>
+        <v>16.09640502929688</v>
       </c>
       <c r="C17" t="n">
         <v>25.67000007629395</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>16.63841247558594</v>
+        <v>16.63841819763184</v>
       </c>
       <c r="C18" t="n">
         <v>26.43000030517578</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>16.17885398864746</v>
+        <v>16.17885589599609</v>
       </c>
       <c r="C19" t="n">
         <v>25.70000076293945</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>16.40548515319824</v>
+        <v>16.40549850463867</v>
       </c>
       <c r="C20" t="n">
         <v>26.05999946594238</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>16.84572219848633</v>
+        <v>16.8457202911377</v>
       </c>
       <c r="C21" t="n">
         <v>26.65500068664551</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>18.02438354492188</v>
+        <v>18.02439498901367</v>
       </c>
       <c r="C22" t="n">
         <v>28.52000045776367</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>19.83819389343262</v>
+        <v>19.83819961547852</v>
       </c>
       <c r="C23" t="n">
         <v>31.38999938964844</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>19.86300086975098</v>
+        <v>19.86300277709961</v>
       </c>
       <c r="C24" t="n">
         <v>31.31999969482422</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>19.85983276367188</v>
+        <v>19.85983085632324</v>
       </c>
       <c r="C25" t="n">
         <v>31.31500053405762</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>19.37148857116699</v>
+        <v>19.37149429321289</v>
       </c>
       <c r="C26" t="n">
         <v>30.54500007629395</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>19.86674690246582</v>
+        <v>19.86674499511719</v>
       </c>
       <c r="C27" t="n">
         <v>31.20499992370605</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>20.67529487609863</v>
+        <v>20.67529678344727</v>
       </c>
       <c r="C28" t="n">
         <v>32.47499847412109</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>21.22281646728516</v>
+        <v>21.22281837463379</v>
       </c>
       <c r="C29" t="n">
         <v>33.33499908447266</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>21.44553375244141</v>
+        <v>21.44553565979004</v>
       </c>
       <c r="C30" t="n">
         <v>33.56499862670898</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>20.06225204467773</v>
+        <v>20.06225967407227</v>
       </c>
       <c r="C31" t="n">
         <v>31.39999961853027</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.76532745361328</v>
+        <v>17.76531982421875</v>
       </c>
       <c r="C32" t="n">
         <v>27.80500030517578</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>18.19247817993164</v>
+        <v>18.19248008728027</v>
       </c>
       <c r="C33" t="n">
         <v>28.35000038146973</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>18.85023307800293</v>
+        <v>18.8502368927002</v>
       </c>
       <c r="C34" t="n">
         <v>29.375</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>14.20745277404785</v>
+        <v>14.20745849609375</v>
       </c>
       <c r="C35" t="n">
         <v>22.13999938964844</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>14.94144058227539</v>
+        <v>14.94143962860107</v>
       </c>
       <c r="C36" t="n">
         <v>23.14999961853027</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.79298782348633</v>
+        <v>14.79298400878906</v>
       </c>
       <c r="C37" t="n">
         <v>22.92000007629395</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>7.490078926086426</v>
+        <v>7.490079879760742</v>
       </c>
       <c r="C38" t="n">
         <v>11.60499954223633</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>5.478043079376221</v>
+        <v>5.478044986724854</v>
       </c>
       <c r="C39" t="n">
         <v>8.380000114440918</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>6.327857971191406</v>
+        <v>6.327854633331299</v>
       </c>
       <c r="C40" t="n">
         <v>9.680000305175781</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.44275951385498</v>
+        <v>9.442758560180664</v>
       </c>
       <c r="C41" t="n">
         <v>14.44499969482422</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.70523071289062</v>
+        <v>11.70522880554199</v>
       </c>
       <c r="C42" t="n">
         <v>17.75</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.25113964080811</v>
+        <v>10.25114250183105</v>
       </c>
       <c r="C43" t="n">
         <v>15.54500007629395</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>12.48337078094482</v>
+        <v>12.48337745666504</v>
       </c>
       <c r="C44" t="n">
         <v>18.93000030517578</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>14.18688583374023</v>
+        <v>14.1868782043457</v>
       </c>
       <c r="C46" t="n">
         <v>21.3700008392334</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>13.77196311950684</v>
+        <v>13.77196025848389</v>
       </c>
       <c r="C47" t="n">
         <v>20.7450008392334</v>
@@ -1374,7 +1386,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>15.44886684417725</v>
+        <v>15.44887447357178</v>
       </c>
       <c r="C49" t="n">
         <v>23.125</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>16.17705154418945</v>
+        <v>16.17705726623535</v>
       </c>
       <c r="C50" t="n">
         <v>24.21500015258789</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>16.61652183532715</v>
+        <v>16.61652755737305</v>
       </c>
       <c r="C51" t="n">
         <v>24.72500038146973</v>
@@ -1474,7 +1486,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>17.12392997741699</v>
+        <v>17.12392425537109</v>
       </c>
       <c r="C53" t="n">
         <v>25.47999954223633</v>
@@ -1524,7 +1536,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.42626476287842</v>
+        <v>14.42626571655273</v>
       </c>
       <c r="C55" t="n">
         <v>21.33499908447266</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>16.63061141967773</v>
+        <v>16.63060760498047</v>
       </c>
       <c r="C56" t="n">
         <v>24.59499931335449</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>16.06892013549805</v>
+        <v>16.06891632080078</v>
       </c>
       <c r="C57" t="n">
         <v>23.625</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>17.58570098876953</v>
+        <v>17.58570671081543</v>
       </c>
       <c r="C58" t="n">
         <v>25.85499954223633</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>19.00723648071289</v>
+        <v>19.00724029541016</v>
       </c>
       <c r="C59" t="n">
         <v>27.94499969482422</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>17.6109504699707</v>
+        <v>17.61094284057617</v>
       </c>
       <c r="C60" t="n">
         <v>25.75</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>19.29680824279785</v>
+        <v>19.29681587219238</v>
       </c>
       <c r="C61" t="n">
         <v>28.21500015258789</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>19.69006538391113</v>
+        <v>19.69007110595703</v>
       </c>
       <c r="C62" t="n">
         <v>28.79000091552734</v>
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>20.23487854003906</v>
+        <v>20.2348804473877</v>
       </c>
       <c r="C63" t="n">
         <v>29.43000030517578</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>18.14470291137695</v>
+        <v>18.14470100402832</v>
       </c>
       <c r="C64" t="n">
         <v>26.38999938964844</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>19.31698226928711</v>
+        <v>19.31698989868164</v>
       </c>
       <c r="C65" t="n">
         <v>28.09499931335449</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>16.52098274230957</v>
+        <v>16.5209846496582</v>
       </c>
       <c r="C66" t="n">
         <v>23.89500045776367</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>16.13726234436035</v>
+        <v>16.13725090026855</v>
       </c>
       <c r="C67" t="n">
         <v>23.34000015258789</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>15.922926902771</v>
+        <v>15.92292404174805</v>
       </c>
       <c r="C68" t="n">
         <v>23.03000068664551</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>13.14537715911865</v>
+        <v>13.14537525177002</v>
       </c>
       <c r="C69" t="n">
         <v>18.86000061035156</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>12.18003749847412</v>
+        <v>12.18003559112549</v>
       </c>
       <c r="C70" t="n">
         <v>17.47500038146973</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>15.71380519866943</v>
+        <v>15.71381378173828</v>
       </c>
       <c r="C71" t="n">
         <v>22.54500007629395</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>15.25094890594482</v>
+        <v>15.25094985961914</v>
       </c>
       <c r="C72" t="n">
         <v>21.71999931335449</v>
@@ -2039,11 +2051,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>15.18775749206543</v>
+        <v>15.18775367736816</v>
       </c>
       <c r="C73" t="n">
         <v>21.6299991607666</v>
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>16.9326286315918</v>
+        <v>16.93263244628906</v>
       </c>
       <c r="C74" t="n">
         <v>24.11499977111816</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>16.70261383056641</v>
+        <v>16.70261764526367</v>
       </c>
       <c r="C75" t="n">
         <v>23.625</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>16.25721740722656</v>
+        <v>16.2572135925293</v>
       </c>
       <c r="C76" t="n">
         <v>22.9950008392334</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>15.9213981628418</v>
+        <v>15.92139053344727</v>
       </c>
       <c r="C77" t="n">
         <v>22.52000045776367</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>14.27671718597412</v>
+        <v>14.27671527862549</v>
       </c>
       <c r="C78" t="n">
         <v>20.04000091552734</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>15.17079162597656</v>
+        <v>15.17078876495361</v>
       </c>
       <c r="C79" t="n">
         <v>21.29500007629395</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>15.5946798324585</v>
+        <v>15.59468555450439</v>
       </c>
       <c r="C80" t="n">
         <v>21.88999938964844</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>16.56879615783691</v>
+        <v>16.56879806518555</v>
       </c>
       <c r="C81" t="n">
         <v>23.09000015258789</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>17.17873573303223</v>
+        <v>17.17873382568359</v>
       </c>
       <c r="C82" t="n">
         <v>23.94000053405762</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.86043167114258</v>
+        <v>17.86043739318848</v>
       </c>
       <c r="C83" t="n">
         <v>24.88999938964844</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>19.14692115783691</v>
+        <v>19.14692306518555</v>
       </c>
       <c r="C84" t="n">
         <v>26.4950008392334</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>19.19389152526855</v>
+        <v>19.19389724731445</v>
       </c>
       <c r="C85" t="n">
         <v>26.55999946594238</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>19.17220878601074</v>
+        <v>19.17221450805664</v>
       </c>
       <c r="C86" t="n">
         <v>26.53000068664551</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>18.1769962310791</v>
+        <v>18.17700576782227</v>
       </c>
       <c r="C87" t="n">
         <v>24.97500038146973</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>18.93028450012207</v>
+        <v>18.9302806854248</v>
       </c>
       <c r="C88" t="n">
         <v>26.01000022888184</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>19.8109245300293</v>
+        <v>19.81093215942383</v>
       </c>
       <c r="C89" t="n">
         <v>27.21999931335449</v>
@@ -2532,7 +2544,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>21.28496360778809</v>
+        <v>21.28495216369629</v>
       </c>
       <c r="C91" t="n">
         <v>29.05999946594238</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>22.58871269226074</v>
+        <v>22.58871078491211</v>
       </c>
       <c r="C92" t="n">
         <v>30.84000015258789</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>21.28716659545898</v>
+        <v>21.28717041015625</v>
       </c>
       <c r="C93" t="n">
         <v>28.89500045776367</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>22.83425712585449</v>
+        <v>22.83426475524902</v>
       </c>
       <c r="C94" t="n">
         <v>30.9950008392334</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>23.93564033508301</v>
+        <v>23.93563461303711</v>
       </c>
       <c r="C95" t="n">
         <v>32.4900016784668</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>24.58243179321289</v>
+        <v>24.58242988586426</v>
       </c>
       <c r="C96" t="n">
         <v>33.18500137329102</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>24.74169731140137</v>
+        <v>24.74169540405273</v>
       </c>
       <c r="C97" t="n">
         <v>33.40000152587891</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>23.25275230407715</v>
+        <v>23.25275421142578</v>
       </c>
       <c r="C98" t="n">
         <v>31.38999938964844</v>
@@ -2793,7 +2805,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2822,7 +2834,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2851,7 +2863,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>22.95208549499512</v>
+        <v>22.95208930969238</v>
       </c>
       <c r="C102" t="n">
         <v>30.61499977111816</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>23.33442878723145</v>
+        <v>23.33443260192871</v>
       </c>
       <c r="C103" t="n">
         <v>31.125</v>
@@ -2938,7 +2950,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>23.09803199768066</v>
+        <v>23.0980396270752</v>
       </c>
       <c r="C105" t="n">
         <v>30.6200008392334</v>
@@ -2996,7 +3008,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>22.52849960327148</v>
+        <v>22.52850914001465</v>
       </c>
       <c r="C107" t="n">
         <v>29.86499977111816</v>
@@ -3054,7 +3066,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>23.19397354125977</v>
+        <v>23.19396781921387</v>
       </c>
       <c r="C109" t="n">
         <v>30.54500007629395</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>21.67150115966797</v>
+        <v>21.67149925231934</v>
       </c>
       <c r="C110" t="n">
         <v>28.54000091552734</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>23.7844123840332</v>
+        <v>23.78440856933594</v>
       </c>
       <c r="C111" t="n">
         <v>31.125</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>24.45687294006348</v>
+        <v>24.45687484741211</v>
       </c>
       <c r="C112" t="n">
         <v>32.00500106811523</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>24.08625411987305</v>
+        <v>24.08625602722168</v>
       </c>
       <c r="C113" t="n">
         <v>31.52000045776367</v>
@@ -3228,7 +3240,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>23.91177177429199</v>
+        <v>23.91177558898926</v>
       </c>
       <c r="C115" t="n">
         <v>31.10000038146973</v>
@@ -3286,11 +3298,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>24.62298011779785</v>
+        <v>24.62297821044922</v>
       </c>
       <c r="C116" t="n">
         <v>32.02500152587891</v>
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>22.66430282592773</v>
+        <v>22.66429710388184</v>
       </c>
       <c r="C117" t="n">
         <v>29.29999923706055</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>22.48252296447754</v>
+        <v>22.48252487182617</v>
       </c>
       <c r="C118" t="n">
         <v>29.06500053405762</v>
@@ -3373,7 +3385,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>25.39711380004883</v>
+        <v>25.39712333679199</v>
       </c>
       <c r="C120" t="n">
         <v>32.61999893188477</v>
@@ -3431,7 +3443,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>22.56310272216797</v>
+        <v>22.56310653686523</v>
       </c>
       <c r="C122" t="n">
         <v>28.97999954223633</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>23.33682250976562</v>
+        <v>23.33682060241699</v>
       </c>
       <c r="C123" t="n">
         <v>29.76000022888184</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>24.75616645812988</v>
+        <v>24.75616455078125</v>
       </c>
       <c r="C124" t="n">
         <v>31.56999969482422</v>
@@ -3547,11 +3559,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>27.04200744628906</v>
+        <v>27.0420036315918</v>
       </c>
       <c r="C125" t="n">
         <v>34.48500061035156</v>
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>27.39723968505859</v>
+        <v>27.39722633361816</v>
       </c>
       <c r="C126" t="n">
         <v>34.72999954223633</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>28.46219635009766</v>
+        <v>28.46220779418945</v>
       </c>
       <c r="C127" t="n">
         <v>36.08000183105469</v>
@@ -3634,7 +3646,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>29.42448806762695</v>
+        <v>29.42449378967285</v>
       </c>
       <c r="C129" t="n">
         <v>37.09000015258789</v>
@@ -3692,7 +3704,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>27.31821060180664</v>
+        <v>27.3182201385498</v>
       </c>
       <c r="C131" t="n">
         <v>34.43500137329102</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>28.48250007629395</v>
+        <v>28.48250770568848</v>
       </c>
       <c r="C132" t="n">
         <v>35.68999862670898</v>
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>27.77223587036133</v>
+        <v>27.7722339630127</v>
       </c>
       <c r="C133" t="n">
         <v>34.79999923706055</v>
@@ -3808,11 +3820,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>27.92786598205566</v>
+        <v>27.9278621673584</v>
       </c>
       <c r="C134" t="n">
         <v>34.99499893188477</v>
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>29.04805183410645</v>
+        <v>29.04804992675781</v>
       </c>
       <c r="C135" t="n">
         <v>36.17499923706055</v>
@@ -3866,7 +3878,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>30.06383514404297</v>
+        <v>30.06382751464844</v>
       </c>
       <c r="C137" t="n">
         <v>37.43999862670898</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>30.44178771972656</v>
+        <v>30.4417724609375</v>
       </c>
       <c r="C138" t="n">
         <v>37.68999862670898</v>
@@ -3953,11 +3965,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>31.3706169128418</v>
+        <v>31.37062644958496</v>
       </c>
       <c r="C139" t="n">
         <v>38.84000015258789</v>
@@ -3982,11 +3994,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>32.20658874511719</v>
+        <v>32.20658111572266</v>
       </c>
       <c r="C140" t="n">
         <v>39.875</v>
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>33.51786041259766</v>
+        <v>33.51784896850586</v>
       </c>
       <c r="C141" t="n">
         <v>41.27500152587891</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>33.04687118530273</v>
+        <v>33.04686737060547</v>
       </c>
       <c r="C142" t="n">
         <v>40.69499969482422</v>
@@ -4069,11 +4081,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>34.06194686889648</v>
+        <v>34.06193161010742</v>
       </c>
       <c r="C143" t="n">
         <v>41.94499969482422</v>
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>35.77532196044922</v>
+        <v>35.77530288696289</v>
       </c>
       <c r="C144" t="n">
         <v>43.81999969482422</v>
@@ -4127,11 +4139,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>35.83244705200195</v>
+        <v>35.83245086669922</v>
       </c>
       <c r="C145" t="n">
         <v>43.88999938964844</v>
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>36.0038948059082</v>
+        <v>36.00389099121094</v>
       </c>
       <c r="C146" t="n">
         <v>44.09999847412109</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>36.49314880371094</v>
+        <v>36.49313735961914</v>
       </c>
       <c r="C147" t="n">
         <v>44.43999862670898</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>35.93475341796875</v>
+        <v>35.93474197387695</v>
       </c>
       <c r="C148" t="n">
         <v>43.7599983215332</v>
@@ -4243,7 +4255,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>37.21377182006836</v>
+        <v>37.21376800537109</v>
       </c>
       <c r="C150" t="n">
         <v>45.06000137329102</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>35.52900314331055</v>
+        <v>35.52899551391602</v>
       </c>
       <c r="C151" t="n">
         <v>43.02000045776367</v>
@@ -4330,11 +4342,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>38.43606948852539</v>
+        <v>38.43606185913086</v>
       </c>
       <c r="C152" t="n">
         <v>46.54000091552734</v>
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>38.40173721313477</v>
+        <v>38.4017219543457</v>
       </c>
       <c r="C153" t="n">
         <v>46.2400016784668</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>39.09103775024414</v>
+        <v>39.09103393554688</v>
       </c>
       <c r="C154" t="n">
         <v>47.06999969482422</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>35.76909255981445</v>
+        <v>35.76908493041992</v>
       </c>
       <c r="C155" t="n">
         <v>43.06999969482422</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>38.2054328918457</v>
+        <v>38.20542526245117</v>
       </c>
       <c r="C156" t="n">
         <v>45.7400016784668</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>38.05509567260742</v>
+        <v>38.05509185791016</v>
       </c>
       <c r="C157" t="n">
         <v>45.56000137329102</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>39.84255981445312</v>
+        <v>39.84256744384766</v>
       </c>
       <c r="C158" t="n">
         <v>47.70000076293945</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>41.271484375</v>
+        <v>41.27148056030273</v>
       </c>
       <c r="C159" t="n">
         <v>49.13999938964844</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>41.99377822875977</v>
+        <v>41.9937744140625</v>
       </c>
       <c r="C160" t="n">
         <v>50</v>
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>42.31293869018555</v>
+        <v>42.31295013427734</v>
       </c>
       <c r="C161" t="n">
         <v>50.38000106811523</v>
@@ -4620,11 +4632,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>43.30981063842773</v>
+        <v>43.3098030090332</v>
       </c>
       <c r="C162" t="n">
         <v>51.29999923706055</v>
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>46.27310180664062</v>
+        <v>46.27310943603516</v>
       </c>
       <c r="C163" t="n">
         <v>54.81000137329102</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>44.44109344482422</v>
+        <v>44.44108963012695</v>
       </c>
       <c r="C164" t="n">
         <v>52.63999938964844</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>42.58249282836914</v>
+        <v>42.58249664306641</v>
       </c>
       <c r="C165" t="n">
         <v>50.18000030517578</v>
@@ -4736,11 +4748,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>44.39847946166992</v>
+        <v>44.39849472045898</v>
       </c>
       <c r="C166" t="n">
         <v>52.31999969482422</v>
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>45.11129760742188</v>
+        <v>45.11130523681641</v>
       </c>
       <c r="C167" t="n">
         <v>53.15999984741211</v>
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>46.76911926269531</v>
+        <v>46.76912307739258</v>
       </c>
       <c r="C168" t="n">
         <v>54.84000015258789</v>
@@ -4823,11 +4835,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>45.11463165283203</v>
+        <v>45.1146240234375</v>
       </c>
       <c r="C169" t="n">
         <v>52.90000152587891</v>
@@ -4852,11 +4864,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>43.98037338256836</v>
+        <v>43.98037719726562</v>
       </c>
       <c r="C170" t="n">
         <v>51.56999969482422</v>
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>36.73848724365234</v>
+        <v>36.73849487304688</v>
       </c>
       <c r="C171" t="n">
         <v>42.84999847412109</v>
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>29.35650444030762</v>
+        <v>29.35649871826172</v>
       </c>
       <c r="C172" t="n">
         <v>34.2400016784668</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>31.92862701416016</v>
+        <v>31.92861938476562</v>
       </c>
       <c r="C173" t="n">
         <v>37.2400016784668</v>
@@ -4968,7 +4980,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4997,11 +5009,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>31.14212608337402</v>
+        <v>31.14212799072266</v>
       </c>
       <c r="C175" t="n">
         <v>36.02999877929688</v>
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>30.74453163146973</v>
+        <v>30.74452972412109</v>
       </c>
       <c r="C176" t="n">
         <v>35.56999969482422</v>
@@ -5055,11 +5067,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>31.62921333312988</v>
+        <v>31.62920570373535</v>
       </c>
       <c r="C177" t="n">
         <v>36.31999969482422</v>
@@ -5084,11 +5096,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>31.65532875061035</v>
+        <v>31.65533065795898</v>
       </c>
       <c r="C178" t="n">
         <v>36.34999847412109</v>
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>29.56529998779297</v>
+        <v>29.56529426574707</v>
       </c>
       <c r="C179" t="n">
         <v>33.95000076293945</v>
@@ -5142,11 +5154,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>38.50575637817383</v>
+        <v>38.50576019287109</v>
       </c>
       <c r="C180" t="n">
         <v>43.93000030517578</v>
@@ -5171,11 +5183,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>38.97908020019531</v>
+        <v>38.97909164428711</v>
       </c>
       <c r="C181" t="n">
         <v>44.47000122070312</v>
@@ -5200,11 +5212,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>39.60141372680664</v>
+        <v>39.60141754150391</v>
       </c>
       <c r="C182" t="n">
         <v>45.18000030517578</v>
@@ -5229,7 +5241,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5258,11 +5270,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>45.17832183837891</v>
+        <v>45.17831802368164</v>
       </c>
       <c r="C184" t="n">
         <v>51.18000030517578</v>
@@ -5287,11 +5299,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>47.42929077148438</v>
+        <v>47.42928695678711</v>
       </c>
       <c r="C185" t="n">
         <v>53.72999954223633</v>
@@ -5316,11 +5328,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>50.32772445678711</v>
+        <v>50.32773208618164</v>
       </c>
       <c r="C186" t="n">
         <v>56.68000030517578</v>
@@ -5345,11 +5357,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>47.64617538452148</v>
+        <v>47.64617919921875</v>
       </c>
       <c r="C187" t="n">
         <v>53.65999984741211</v>
@@ -5374,11 +5386,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>48.83600234985352</v>
+        <v>48.83601379394531</v>
       </c>
       <c r="C188" t="n">
         <v>55</v>
@@ -5403,11 +5415,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>50.61812210083008</v>
+        <v>50.61812591552734</v>
       </c>
       <c r="C189" t="n">
         <v>56.68000030517578</v>
@@ -5432,11 +5444,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>46.55475234985352</v>
+        <v>46.55474853515625</v>
       </c>
       <c r="C190" t="n">
         <v>52.13000106811523</v>
@@ -5461,11 +5473,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>47.93003082275391</v>
+        <v>47.93004608154297</v>
       </c>
       <c r="C191" t="n">
         <v>53.66999816894531</v>
@@ -5490,7 +5502,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5519,11 +5531,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>52.44587326049805</v>
+        <v>52.44586944580078</v>
       </c>
       <c r="C193" t="n">
         <v>58.38999938964844</v>
@@ -5548,11 +5560,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>56.42490005493164</v>
+        <v>56.42488861083984</v>
       </c>
       <c r="C194" t="n">
         <v>62.81999969482422</v>
@@ -5577,7 +5589,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5606,11 +5618,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>58.19755554199219</v>
+        <v>58.19754791259766</v>
       </c>
       <c r="C196" t="n">
         <v>64.38999938964844</v>
@@ -5635,11 +5647,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>51.77133178710938</v>
+        <v>51.77132797241211</v>
       </c>
       <c r="C197" t="n">
         <v>57.27999877929688</v>
@@ -5664,11 +5676,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>55.13742446899414</v>
+        <v>55.13743209838867</v>
       </c>
       <c r="C198" t="n">
         <v>60.56999969482422</v>
@@ -5693,11 +5705,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>50.36742401123047</v>
+        <v>50.36741638183594</v>
       </c>
       <c r="C199" t="n">
         <v>55.33000183105469</v>
@@ -5722,7 +5734,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5751,11 +5763,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>54.44062423706055</v>
+        <v>54.44062042236328</v>
       </c>
       <c r="C201" t="n">
         <v>59.41999816894531</v>
@@ -5780,11 +5792,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>51.49045562744141</v>
+        <v>51.49046325683594</v>
       </c>
       <c r="C202" t="n">
         <v>56.20000076293945</v>
@@ -5809,7 +5821,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5838,11 +5850,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>66.28818511962891</v>
+        <v>66.28819274902344</v>
       </c>
       <c r="C204" t="n">
         <v>71.93000030517578</v>
@@ -5867,11 +5879,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>66.29741668701172</v>
+        <v>66.29740905761719</v>
       </c>
       <c r="C205" t="n">
         <v>71.94000244140625</v>
@@ -5896,11 +5908,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>67.73504638671875</v>
+        <v>67.73503875732422</v>
       </c>
       <c r="C206" t="n">
         <v>73.5</v>
@@ -5925,11 +5937,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>63.1783561706543</v>
+        <v>63.17836761474609</v>
       </c>
       <c r="C207" t="n">
         <v>68.15000152587891</v>
@@ -5954,11 +5966,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>59.81317520141602</v>
+        <v>59.81317138671875</v>
       </c>
       <c r="C208" t="n">
         <v>64.51999664306641</v>
@@ -5983,11 +5995,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>64.75432586669922</v>
+        <v>64.75433349609375</v>
       </c>
       <c r="C209" t="n">
         <v>69.84999847412109</v>
@@ -6012,7 +6024,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6041,11 +6053,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>65.12184143066406</v>
+        <v>65.12183380126953</v>
       </c>
       <c r="C211" t="n">
         <v>69.80000305175781</v>
@@ -6070,11 +6082,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>67.49159240722656</v>
+        <v>67.49160766601562</v>
       </c>
       <c r="C212" t="n">
         <v>72.33999633789062</v>
@@ -6099,11 +6111,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>69.96684265136719</v>
+        <v>69.96682739257812</v>
       </c>
       <c r="C213" t="n">
         <v>74.56999969482422</v>
@@ -6128,11 +6140,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>72.01226806640625</v>
+        <v>72.01227569580078</v>
       </c>
       <c r="C214" t="n">
         <v>76.75</v>
@@ -6157,11 +6169,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>73.288330078125</v>
+        <v>73.28831481933594</v>
       </c>
       <c r="C215" t="n">
         <v>78.11000061035156</v>
@@ -6186,11 +6198,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>78.00669860839844</v>
+        <v>78.00670623779297</v>
       </c>
       <c r="C216" t="n">
         <v>82.70999908447266</v>
@@ -6215,11 +6227,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>77.80865478515625</v>
+        <v>77.80866241455078</v>
       </c>
       <c r="C217" t="n">
         <v>82.5</v>
@@ -6244,11 +6256,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>79.54402160644531</v>
+        <v>79.54401397705078</v>
       </c>
       <c r="C218" t="n">
         <v>84.33999633789062</v>
@@ -6273,11 +6285,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>76.63141632080078</v>
+        <v>76.63143157958984</v>
       </c>
       <c r="C219" t="n">
         <v>80.73999786376953</v>
@@ -6302,11 +6314,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>81.49087524414062</v>
+        <v>81.49089050292969</v>
       </c>
       <c r="C220" t="n">
         <v>85.86000061035156</v>
@@ -6331,11 +6343,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>79.39333343505859</v>
+        <v>79.39334869384766</v>
       </c>
       <c r="C221" t="n">
         <v>83.65000152587891</v>
@@ -6360,11 +6372,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>85.78598022460938</v>
+        <v>85.78596496582031</v>
       </c>
       <c r="C222" t="n">
         <v>89.87000274658203</v>
@@ -6389,11 +6401,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>85.25142669677734</v>
+        <v>85.25141906738281</v>
       </c>
       <c r="C223" t="n">
         <v>89.30999755859375</v>
@@ -6418,11 +6430,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>91.04557037353516</v>
+        <v>91.04557800292969</v>
       </c>
       <c r="C224" t="n">
         <v>95.37999725341797</v>
@@ -6447,11 +6459,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>105.8498306274414</v>
+        <v>105.8498458862305</v>
       </c>
       <c r="C225" t="n">
         <v>110.3600006103516</v>
@@ -6476,11 +6488,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>107.2309951782227</v>
+        <v>107.2310028076172</v>
       </c>
       <c r="C226" t="n">
         <v>111.8000030517578</v>
@@ -6505,11 +6517,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>100.5074768066406</v>
+        <v>100.5074844360352</v>
       </c>
       <c r="C227" t="n">
         <v>104.7900009155273</v>
@@ -6534,7 +6546,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6563,11 +6575,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>99.66105651855469</v>
+        <v>99.66104125976562</v>
       </c>
       <c r="C229" t="n">
         <v>103.4400024414062</v>
@@ -6592,11 +6604,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>103.4570999145508</v>
+        <v>103.4571151733398</v>
       </c>
       <c r="C230" t="n">
         <v>107.379997253418</v>
@@ -6621,11 +6633,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>106.0607757568359</v>
+        <v>106.0607833862305</v>
       </c>
       <c r="C231" t="n">
         <v>109.4700012207031</v>
@@ -6650,7 +6662,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6679,7 +6691,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6708,11 +6720,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>100.8693695068359</v>
+        <v>100.8693542480469</v>
       </c>
       <c r="C234" t="n">
         <v>103.5400009155273</v>
@@ -6737,7 +6749,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6766,11 +6778,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>96.79718017578125</v>
+        <v>96.79717254638672</v>
       </c>
       <c r="C236" t="n">
         <v>99.36000061035156</v>
@@ -6795,7 +6807,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6824,7 +6836,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6853,11 +6865,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>104.9949493408203</v>
+        <v>104.9949340820312</v>
       </c>
       <c r="C239" t="n">
         <v>107.1900024414062</v>
@@ -6882,7 +6894,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6911,7 +6923,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6940,7 +6952,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6969,7 +6981,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6998,7 +7010,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7027,7 +7039,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7056,7 +7068,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7085,7 +7097,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7114,7 +7126,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7143,7 +7155,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7172,32 +7184,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>115.2300033569336</v>
+        <v>114.0100021362305</v>
       </c>
       <c r="C250" t="n">
-        <v>115.2300033569336</v>
+        <v>114.0100021362305</v>
       </c>
       <c r="D250" t="n">
-        <v>37455900</v>
+        <v>39056300</v>
       </c>
       <c r="E250" t="n">
         <v>9.27</v>
       </c>
       <c r="F250" t="n">
-        <v>12.43042107410287</v>
+        <v>12.29881360692885</v>
       </c>
       <c r="G250" t="n">
         <v>501343298</v>
       </c>
       <c r="H250" t="n">
-        <v>57769789911.51616</v>
+        <v>57158150475.96483</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07471108150726691</v>
+        <v>0.07790330529161676</v>
       </c>
     </row>
   </sheetData>
@@ -7229,75 +7241,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7333,13 +7345,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7417,13 +7429,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7459,13 +7471,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7534,7 +7546,7 @@
       <c r="I7" t="n">
         <v>1.595</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K7" t="n">
@@ -7547,13 +7559,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7580,7 +7592,7 @@
       <c r="I8" t="n">
         <v>1.66</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K8" t="n">
@@ -7593,13 +7605,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7626,7 +7638,7 @@
       <c r="I9" t="n">
         <v>1.94</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K9" t="n">
@@ -7639,13 +7651,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7672,7 +7684,7 @@
       <c r="I10" t="n">
         <v>2.285</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7685,13 +7697,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7718,7 +7730,7 @@
       <c r="I11" t="n">
         <v>2.48</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K11" t="n">
@@ -7731,13 +7743,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7764,7 +7776,7 @@
       <c r="I12" t="n">
         <v>2.225</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K12" t="n">
@@ -7777,13 +7789,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7810,7 +7822,7 @@
       <c r="I13" t="n">
         <v>1.91</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K13" t="n">
@@ -7823,13 +7835,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7856,7 +7868,7 @@
       <c r="I14" t="n">
         <v>1.975</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K14" t="n">
@@ -7869,13 +7881,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7902,7 +7914,7 @@
       <c r="I15" t="n">
         <v>2.1</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="K15" t="n">
@@ -7915,13 +7927,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7948,7 +7960,7 @@
       <c r="I16" t="n">
         <v>2.52</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="K16" t="n">
@@ -7961,13 +7973,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7994,7 +8006,7 @@
       <c r="I17" t="n">
         <v>2.734999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="K17" t="n">
@@ -8007,13 +8019,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8040,7 +8052,7 @@
       <c r="I18" t="n">
         <v>3.02</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K18" t="n">
@@ -8053,13 +8065,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8086,7 +8098,7 @@
       <c r="I19" t="n">
         <v>3.055</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="K19" t="n">
@@ -8099,13 +8111,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8132,7 +8144,7 @@
       <c r="I20" t="n">
         <v>3.165</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="K20" t="n">
@@ -8145,13 +8157,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8178,7 +8190,7 @@
       <c r="I21" t="n">
         <v>3.6</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K21" t="n">
@@ -8191,13 +8203,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8224,7 +8236,7 @@
       <c r="I22" t="n">
         <v>3.27</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K22" t="n">
@@ -8237,13 +8249,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8270,7 +8282,7 @@
       <c r="I23" t="n">
         <v>3.375</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K23" t="n">
@@ -8283,13 +8295,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8316,7 +8328,7 @@
       <c r="I24" t="n">
         <v>3.225</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="K24" t="n">
@@ -8329,13 +8341,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8362,7 +8374,7 @@
       <c r="I25" t="n">
         <v>3.165</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="K25" t="n">
@@ -8375,13 +8387,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8408,7 +8420,7 @@
       <c r="I26" t="n">
         <v>3.195</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="K26" t="n">
@@ -8421,13 +8433,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8454,7 +8466,7 @@
       <c r="I27" t="n">
         <v>3.255</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="K27" t="n">
@@ -8467,13 +8479,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8500,7 +8512,7 @@
       <c r="I28" t="n">
         <v>3.21</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="K28" t="n">
@@ -8513,13 +8525,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8546,7 +8558,7 @@
       <c r="I29" t="n">
         <v>2.98</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K29" t="n">
@@ -8559,13 +8571,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8592,7 +8604,7 @@
       <c r="I30" t="n">
         <v>2.86</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="K30" t="n">
@@ -8605,13 +8617,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8638,7 +8650,7 @@
       <c r="I31" t="n">
         <v>2.93</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K31" t="n">
@@ -8651,13 +8663,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8684,7 +8696,7 @@
       <c r="I32" t="n">
         <v>3.045</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K32" t="n">
@@ -8697,13 +8709,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8730,7 +8742,7 @@
       <c r="I33" t="n">
         <v>3.045</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K33" t="n">
@@ -8743,13 +8755,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8776,7 +8788,7 @@
       <c r="I34" t="n">
         <v>3.149999999999999</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="K34" t="n">
@@ -8789,13 +8801,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8822,7 +8834,7 @@
       <c r="I35" t="n">
         <v>3.215</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="K35" t="n">
@@ -8835,13 +8847,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8868,7 +8880,7 @@
       <c r="I36" t="n">
         <v>3.08</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K36" t="n">
@@ -8881,13 +8893,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8914,7 +8926,7 @@
       <c r="I37" t="n">
         <v>3.315</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K37" t="n">
@@ -8927,13 +8939,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8960,7 +8972,7 @@
       <c r="I38" t="n">
         <v>3.45</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K38" t="n">
@@ -8973,13 +8985,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9006,7 +9018,7 @@
       <c r="I39" t="n">
         <v>5.8</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="K39" t="n">
@@ -9019,13 +9031,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9052,7 +9064,7 @@
       <c r="I40" t="n">
         <v>5.975</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="K40" t="n">
@@ -9065,13 +9077,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9098,7 +9110,7 @@
       <c r="I41" t="n">
         <v>6.15</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="K41" t="n">
@@ -9111,13 +9123,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9144,7 +9156,7 @@
       <c r="I42" t="n">
         <v>6.34</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="K42" t="n">
@@ -9157,13 +9169,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9190,7 +9202,7 @@
       <c r="I43" t="n">
         <v>3.76</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="K43" t="n">
@@ -9203,13 +9215,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9236,7 +9248,7 @@
       <c r="I44" t="n">
         <v>4.079999999999999</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="K44" t="n">
@@ -9249,13 +9261,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9282,7 +9294,7 @@
       <c r="I45" t="n">
         <v>4.1</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K45" t="n">
@@ -9295,13 +9307,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9328,7 +9340,7 @@
       <c r="I46" t="n">
         <v>4.05</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="K46" t="n">
@@ -9341,13 +9353,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9374,7 +9386,7 @@
       <c r="I47" t="n">
         <v>4.42</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="K47" t="n">
@@ -9387,13 +9399,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9420,7 +9432,7 @@
       <c r="I48" t="n">
         <v>3.97</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="K48" t="n">
@@ -9433,13 +9445,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9466,7 +9478,7 @@
       <c r="I49" t="n">
         <v>4</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="K49" t="n">
@@ -9479,13 +9491,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9512,7 +9524,7 @@
       <c r="I50" t="n">
         <v>6.399999999999999</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="K50" t="n">
@@ -9525,13 +9537,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9558,7 +9570,7 @@
       <c r="I51" t="n">
         <v>6.69</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="K51" t="n">
@@ -9571,13 +9583,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9604,7 +9616,7 @@
       <c r="I52" t="n">
         <v>7.779999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K52" t="n">
@@ -9617,13 +9629,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9650,7 +9662,7 @@
       <c r="I53" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="K53" t="n">
@@ -9663,13 +9675,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9696,7 +9708,7 @@
       <c r="I54" t="n">
         <v>6.159999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K54" t="n">
@@ -9709,13 +9721,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9742,7 +9754,7 @@
       <c r="I55" t="n">
         <v>6.389999999999998</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="K55" t="n">
@@ -9755,13 +9767,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9788,7 +9800,7 @@
       <c r="I56" t="n">
         <v>6.099999999999998</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K56" t="n">
@@ -9801,13 +9813,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9834,7 +9846,7 @@
       <c r="I57" t="n">
         <v>6.639999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="K57" t="n">
@@ -9847,13 +9859,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9880,7 +9892,7 @@
       <c r="I58" t="n">
         <v>7.849999999999998</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="K58" t="n">
@@ -9893,13 +9905,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9926,7 +9938,7 @@
       <c r="I59" t="n">
         <v>6.59</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="K59" t="n">
@@ -9939,13 +9951,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9972,7 +9984,7 @@
       <c r="I60" t="n">
         <v>6.949999999999999</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="K60" t="n">
@@ -9985,13 +9997,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10018,7 +10030,7 @@
       <c r="I61" t="n">
         <v>7.499999999999999</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="K61" t="n">
@@ -10031,13 +10043,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10064,7 +10076,7 @@
       <c r="I62" t="n">
         <v>7.609999999999999</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K62" t="n">
@@ -10077,13 +10089,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10110,7 +10122,7 @@
       <c r="I63" t="n">
         <v>7.749999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="K63" t="n">
@@ -10123,13 +10135,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10156,7 +10168,7 @@
       <c r="I64" t="n">
         <v>9.059999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K64" t="n">
@@ -10169,13 +10181,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10202,7 +10214,7 @@
       <c r="I65" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K65" t="n">
@@ -10215,13 +10227,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10248,7 +10260,7 @@
       <c r="I66" t="n">
         <v>6.639999999999999</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K66" t="n">
@@ -10261,13 +10273,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10294,7 +10306,7 @@
       <c r="I67" t="n">
         <v>9.629999999999999</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="K67" t="n">
@@ -10307,13 +10319,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10340,7 +10352,7 @@
       <c r="I68" t="n">
         <v>6.43</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="K68" t="n">
@@ -10353,13 +10365,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10386,7 +10398,7 @@
       <c r="I69" t="n">
         <v>4.44</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K69" t="n">
@@ -10399,13 +10411,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10432,7 +10444,7 @@
       <c r="I70" t="n">
         <v>7.69</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="K70" t="n">
@@ -10445,13 +10457,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10478,7 +10490,7 @@
       <c r="I71" t="n">
         <v>6.819999999999999</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="K71" t="n">
@@ -10491,13 +10503,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10524,7 +10536,7 @@
       <c r="I72" t="n">
         <v>8.75</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="K72" t="n">
@@ -10537,13 +10549,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10570,7 +10582,7 @@
       <c r="I73" t="n">
         <v>9.27</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="K73" t="n">
@@ -10607,52 +10619,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40029</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="C2" t="n">
@@ -10681,10 +10693,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40120</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10713,10 +10725,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40231</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40301</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40388</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C6" t="n">
@@ -10809,10 +10821,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40479</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10841,10 +10853,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40602</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10873,10 +10885,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40661</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C9" t="n">
@@ -10905,10 +10917,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40752</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -10937,10 +10949,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40843</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C11" t="n">
@@ -10969,10 +10981,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40968</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40966</v>
       </c>
       <c r="C12" t="n">
@@ -11001,10 +11013,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41026</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="C13" t="n">
@@ -11033,10 +11045,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41117</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C14" t="n">
@@ -11065,10 +11077,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41208</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C15" t="n">
@@ -11097,10 +11109,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41324</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="C16" t="n">
@@ -11129,10 +11141,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41390</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41400</v>
       </c>
       <c r="C17" t="n">
@@ -11161,10 +11173,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41485</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C18" t="n">
@@ -11193,10 +11205,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41576</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="C19" t="n">
@@ -11225,10 +11237,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41688</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C20" t="n">
@@ -11257,10 +11269,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41753</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41761</v>
       </c>
       <c r="C21" t="n">
@@ -11289,10 +11301,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41848</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="C22" t="n">
@@ -11321,10 +11333,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41939</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41946</v>
       </c>
       <c r="C23" t="n">
@@ -11353,10 +11365,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42052</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42061</v>
       </c>
       <c r="C24" t="n">
@@ -11385,10 +11397,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42118</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42125</v>
       </c>
       <c r="C25" t="n">
@@ -11417,10 +11429,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42212</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C26" t="n">
@@ -11449,10 +11461,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42303</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42311</v>
       </c>
       <c r="C27" t="n">
@@ -11481,10 +11493,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42416</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C28" t="n">
@@ -11513,10 +11525,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42486</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C29" t="n">
@@ -11545,10 +11557,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42579</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C30" t="n">
@@ -11577,10 +11589,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42670</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="C31" t="n">
@@ -11609,10 +11621,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42781</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="C32" t="n">
@@ -11641,10 +11653,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42850</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11673,10 +11685,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42942</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C34" t="n">
@@ -11705,10 +11717,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43033</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C35" t="n">
@@ -11737,10 +11749,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43144</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="C36" t="n">
@@ -11769,10 +11781,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43215</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43224</v>
       </c>
       <c r="C37" t="n">
@@ -11801,10 +11813,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43307</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43315</v>
       </c>
       <c r="C38" t="n">
@@ -11833,10 +11845,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43397</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="C39" t="n">
@@ -11865,10 +11877,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43508</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43521</v>
       </c>
       <c r="C40" t="n">
@@ -11897,10 +11909,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43572</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="C41" t="n">
@@ -11929,10 +11941,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43664</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C42" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43755</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43763</v>
       </c>
       <c r="C43" t="n">
@@ -11993,10 +12005,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43873</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43882</v>
       </c>
       <c r="C44" t="n">
@@ -12025,10 +12037,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43941</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="C45" t="n">
@@ -12057,10 +12069,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44032</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44041</v>
       </c>
       <c r="C46" t="n">
@@ -12089,10 +12101,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44123</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44133</v>
       </c>
       <c r="C47" t="n">
@@ -12121,10 +12133,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44244</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="C48" t="n">
@@ -12153,10 +12165,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44306</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C49" t="n">
@@ -12185,10 +12197,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44397</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44406</v>
       </c>
       <c r="C50" t="n">
@@ -12217,10 +12229,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44488</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C51" t="n">
@@ -12249,10 +12261,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44608</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C52" t="n">
@@ -12281,10 +12293,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44672</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C53" t="n">
@@ -12313,10 +12325,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44767</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="C54" t="n">
@@ -12345,10 +12357,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44858</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44867</v>
       </c>
       <c r="C55" t="n">
@@ -12377,10 +12389,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44973</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44981</v>
       </c>
       <c r="C56" t="n">
@@ -12409,10 +12421,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45037</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="C57" t="n">
@@ -12441,10 +12453,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45133</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45140</v>
       </c>
       <c r="C58" t="n">
@@ -12473,10 +12485,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45225</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C59" t="n">
@@ -12505,10 +12517,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45337</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="C60" t="n">
@@ -12537,10 +12549,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45406</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C61" t="n">
@@ -12569,10 +12581,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45497</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C62" t="n">
@@ -12601,10 +12613,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45589</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C63" t="n">
@@ -12633,10 +12645,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45706</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="C64" t="n">
@@ -12665,10 +12677,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45776</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45784</v>
       </c>
       <c r="C65" t="n">
@@ -12697,10 +12709,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45866</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C66" t="n">
@@ -12729,10 +12741,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45957</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C67" t="n">
@@ -12761,10 +12773,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="C68" t="n">
@@ -12793,10 +12805,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46140</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46148</v>
       </c>
       <c r="C69" t="n">
@@ -12825,10 +12837,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46231</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="C70" t="n">
@@ -12875,12 +12887,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/AFL.xlsx
+++ b/salidas/empresas/AFL.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>14.48772144317627</v>
+        <v>14.48771476745605</v>
       </c>
       <c r="C2" t="n">
         <v>23.47500038146973</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>14.31084537506104</v>
+        <v>14.3108549118042</v>
       </c>
       <c r="C3" t="n">
         <v>23.125</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>13.9642972946167</v>
+        <v>13.96430015563965</v>
       </c>
       <c r="C4" t="n">
         <v>22.56500053405762</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>14.71000480651855</v>
+        <v>14.71000576019287</v>
       </c>
       <c r="C5" t="n">
         <v>23.77000045776367</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>14.51991844177246</v>
+        <v>14.51991367340088</v>
       </c>
       <c r="C6" t="n">
         <v>23.39999961853027</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>14.380295753479</v>
+        <v>14.38029193878174</v>
       </c>
       <c r="C7" t="n">
         <v>23.17499923706055</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>13.69463348388672</v>
+        <v>13.6946382522583</v>
       </c>
       <c r="C8" t="n">
         <v>22.06999969482422</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>14.02539825439453</v>
+        <v>14.02539730072021</v>
       </c>
       <c r="C9" t="n">
         <v>22.53499984741211</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.24011516571045</v>
+        <v>14.24011421203613</v>
       </c>
       <c r="C10" t="n">
         <v>22.8799991607666</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>13.97871971130371</v>
+        <v>13.97871589660645</v>
       </c>
       <c r="C11" t="n">
         <v>22.45999908447266</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>13.78549861907959</v>
+        <v>13.78549766540527</v>
       </c>
       <c r="C12" t="n">
         <v>22.06999969482422</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>14.3664026260376</v>
+        <v>14.36640167236328</v>
       </c>
       <c r="C13" t="n">
         <v>23</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>14.86922836303711</v>
+        <v>14.86922550201416</v>
       </c>
       <c r="C14" t="n">
         <v>23.80500030517578</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>14.75450611114502</v>
+        <v>14.75451183319092</v>
       </c>
       <c r="C16" t="n">
         <v>23.53000068664551</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>16.09640502929688</v>
+        <v>16.09639930725098</v>
       </c>
       <c r="C17" t="n">
         <v>25.67000007629395</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>16.63841819763184</v>
+        <v>16.6384105682373</v>
       </c>
       <c r="C18" t="n">
         <v>26.43000030517578</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>16.17885589599609</v>
+        <v>16.17885971069336</v>
       </c>
       <c r="C19" t="n">
         <v>25.70000076293945</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>16.40549850463867</v>
+        <v>16.40549087524414</v>
       </c>
       <c r="C20" t="n">
         <v>26.05999946594238</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>16.8457202911377</v>
+        <v>16.84572410583496</v>
       </c>
       <c r="C21" t="n">
         <v>26.65500068664551</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>18.02439498901367</v>
+        <v>18.02438354492188</v>
       </c>
       <c r="C22" t="n">
         <v>28.52000045776367</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>19.83819961547852</v>
+        <v>19.83820343017578</v>
       </c>
       <c r="C23" t="n">
         <v>31.38999938964844</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>19.86300277709961</v>
+        <v>19.86299514770508</v>
       </c>
       <c r="C24" t="n">
         <v>31.31999969482422</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>19.85983085632324</v>
+        <v>19.85982322692871</v>
       </c>
       <c r="C25" t="n">
         <v>31.31500053405762</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>19.37149429321289</v>
+        <v>19.37149810791016</v>
       </c>
       <c r="C26" t="n">
         <v>30.54500007629395</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>19.86674499511719</v>
+        <v>19.86675643920898</v>
       </c>
       <c r="C27" t="n">
         <v>31.20499992370605</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>20.67529678344727</v>
+        <v>20.67530059814453</v>
       </c>
       <c r="C28" t="n">
         <v>32.47499847412109</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>21.22281837463379</v>
+        <v>21.22282409667969</v>
       </c>
       <c r="C29" t="n">
         <v>33.33499908447266</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>21.44553565979004</v>
+        <v>21.44552993774414</v>
       </c>
       <c r="C30" t="n">
         <v>33.56499862670898</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>20.06225967407227</v>
+        <v>20.0622615814209</v>
       </c>
       <c r="C31" t="n">
         <v>31.39999961853027</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.76531982421875</v>
+        <v>17.76532554626465</v>
       </c>
       <c r="C32" t="n">
         <v>27.80500030517578</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>18.19248008728027</v>
+        <v>18.19247627258301</v>
       </c>
       <c r="C33" t="n">
         <v>28.35000038146973</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>18.8502368927002</v>
+        <v>18.85022926330566</v>
       </c>
       <c r="C34" t="n">
         <v>29.375</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>14.20745849609375</v>
+        <v>14.20746326446533</v>
       </c>
       <c r="C35" t="n">
         <v>22.13999938964844</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>14.94143962860107</v>
+        <v>14.94143676757812</v>
       </c>
       <c r="C36" t="n">
         <v>23.14999961853027</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.79298400878906</v>
+        <v>14.79299163818359</v>
       </c>
       <c r="C37" t="n">
         <v>22.92000007629395</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>7.490079879760742</v>
+        <v>7.490080833435059</v>
       </c>
       <c r="C38" t="n">
         <v>11.60499954223633</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>5.478044986724854</v>
+        <v>5.478041172027588</v>
       </c>
       <c r="C39" t="n">
         <v>8.380000114440918</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>6.327854633331299</v>
+        <v>6.327859878540039</v>
       </c>
       <c r="C40" t="n">
         <v>9.680000305175781</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>9.442758560180664</v>
+        <v>9.442756652832031</v>
       </c>
       <c r="C41" t="n">
         <v>14.44499969482422</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.70522880554199</v>
+        <v>11.70522785186768</v>
       </c>
       <c r="C42" t="n">
         <v>17.75</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.25114250183105</v>
+        <v>10.251145362854</v>
       </c>
       <c r="C43" t="n">
         <v>15.54500007629395</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>12.48337745666504</v>
+        <v>12.48337936401367</v>
       </c>
       <c r="C44" t="n">
         <v>18.93000030517578</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>13.48317527770996</v>
+        <v>13.48317813873291</v>
       </c>
       <c r="C45" t="n">
         <v>20.30999946594238</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>14.1868782043457</v>
+        <v>14.18687343597412</v>
       </c>
       <c r="C46" t="n">
         <v>21.3700008392334</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>13.77196025848389</v>
+        <v>13.77196216583252</v>
       </c>
       <c r="C47" t="n">
         <v>20.7450008392334</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>15.37538719177246</v>
+        <v>15.37538814544678</v>
       </c>
       <c r="C48" t="n">
         <v>23.01499938964844</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>15.44887447357178</v>
+        <v>15.44887065887451</v>
       </c>
       <c r="C49" t="n">
         <v>23.125</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>16.17705726623535</v>
+        <v>16.17705917358398</v>
       </c>
       <c r="C50" t="n">
         <v>24.21500015258789</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>16.61652755737305</v>
+        <v>16.61652183532715</v>
       </c>
       <c r="C51" t="n">
         <v>24.72500038146973</v>
@@ -1490,7 +1490,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>18.24289703369141</v>
+        <v>18.24289131164551</v>
       </c>
       <c r="C52" t="n">
         <v>27.14500045776367</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>17.12392425537109</v>
+        <v>17.12392044067383</v>
       </c>
       <c r="C53" t="n">
         <v>25.47999954223633</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>14.97735404968262</v>
+        <v>14.9773530960083</v>
       </c>
       <c r="C54" t="n">
         <v>22.14999961853027</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>14.42626571655273</v>
+        <v>14.42626953125</v>
       </c>
       <c r="C55" t="n">
         <v>21.33499908447266</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>16.63060760498047</v>
+        <v>16.6306037902832</v>
       </c>
       <c r="C56" t="n">
         <v>24.59499931335449</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>16.06891632080078</v>
+        <v>16.06892395019531</v>
       </c>
       <c r="C57" t="n">
         <v>23.625</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>17.58570671081543</v>
+        <v>17.58568954467773</v>
       </c>
       <c r="C58" t="n">
         <v>25.85499954223633</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>19.00724029541016</v>
+        <v>19.00724220275879</v>
       </c>
       <c r="C59" t="n">
         <v>27.94499969482422</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>17.61094284057617</v>
+        <v>17.6109504699707</v>
       </c>
       <c r="C60" t="n">
         <v>25.75</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>19.29681587219238</v>
+        <v>19.29681396484375</v>
       </c>
       <c r="C61" t="n">
         <v>28.21500015258789</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>19.69007110595703</v>
+        <v>19.6900634765625</v>
       </c>
       <c r="C62" t="n">
         <v>28.79000091552734</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>20.2348804473877</v>
+        <v>20.23487663269043</v>
       </c>
       <c r="C63" t="n">
         <v>29.43000030517578</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>18.14470100402832</v>
+        <v>18.14469528198242</v>
       </c>
       <c r="C64" t="n">
         <v>26.38999938964844</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>19.31698989868164</v>
+        <v>19.31698036193848</v>
       </c>
       <c r="C65" t="n">
         <v>28.09499931335449</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>16.5209846496582</v>
+        <v>16.5209903717041</v>
       </c>
       <c r="C66" t="n">
         <v>23.89500045776367</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>16.13725090026855</v>
+        <v>16.13725852966309</v>
       </c>
       <c r="C67" t="n">
         <v>23.34000015258789</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>13.14537525177002</v>
+        <v>13.14537239074707</v>
       </c>
       <c r="C69" t="n">
         <v>18.86000061035156</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>12.18003559112549</v>
+        <v>12.18003273010254</v>
       </c>
       <c r="C70" t="n">
         <v>17.47500038146973</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>15.71381378173828</v>
+        <v>15.71380996704102</v>
       </c>
       <c r="C71" t="n">
         <v>22.54500007629395</v>
@@ -2026,7 +2026,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>15.25094985961914</v>
+        <v>15.25095558166504</v>
       </c>
       <c r="C72" t="n">
         <v>21.71999931335449</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>15.18775367736816</v>
+        <v>15.18776416778564</v>
       </c>
       <c r="C73" t="n">
         <v>21.6299991607666</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>16.93263244628906</v>
+        <v>16.9326343536377</v>
       </c>
       <c r="C74" t="n">
         <v>24.11499977111816</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>16.70261764526367</v>
+        <v>16.70262336730957</v>
       </c>
       <c r="C75" t="n">
         <v>23.625</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>15.92139053344727</v>
+        <v>15.92139625549316</v>
       </c>
       <c r="C77" t="n">
         <v>22.52000045776367</v>
@@ -2200,7 +2200,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>14.27671527862549</v>
+        <v>14.27671813964844</v>
       </c>
       <c r="C78" t="n">
         <v>20.04000091552734</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>15.17078876495361</v>
+        <v>15.17079734802246</v>
       </c>
       <c r="C79" t="n">
         <v>21.29500007629395</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>15.59468555450439</v>
+        <v>15.59467697143555</v>
       </c>
       <c r="C80" t="n">
         <v>21.88999938964844</v>
@@ -2287,7 +2287,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>16.56879806518555</v>
+        <v>16.56879997253418</v>
       </c>
       <c r="C81" t="n">
         <v>23.09000015258789</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>17.17873382568359</v>
+        <v>17.17874145507812</v>
       </c>
       <c r="C82" t="n">
         <v>23.94000053405762</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>17.86043739318848</v>
+        <v>17.86042785644531</v>
       </c>
       <c r="C83" t="n">
         <v>24.88999938964844</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>19.14692306518555</v>
+        <v>19.14692115783691</v>
       </c>
       <c r="C84" t="n">
         <v>26.4950008392334</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>19.19389724731445</v>
+        <v>19.19389343261719</v>
       </c>
       <c r="C85" t="n">
         <v>26.55999946594238</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>19.17221450805664</v>
+        <v>19.17221260070801</v>
       </c>
       <c r="C86" t="n">
         <v>26.53000068664551</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>18.17700576782227</v>
+        <v>18.17700004577637</v>
       </c>
       <c r="C87" t="n">
         <v>24.97500038146973</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>19.81093215942383</v>
+        <v>19.8109245300293</v>
       </c>
       <c r="C89" t="n">
         <v>27.21999931335449</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>20.3950309753418</v>
+        <v>20.39503479003906</v>
       </c>
       <c r="C90" t="n">
         <v>27.84499931335449</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>21.28495216369629</v>
+        <v>21.28495407104492</v>
       </c>
       <c r="C91" t="n">
         <v>29.05999946594238</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>22.58871078491211</v>
+        <v>22.58871650695801</v>
       </c>
       <c r="C92" t="n">
         <v>30.84000015258789</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>21.28717041015625</v>
+        <v>21.28716659545898</v>
       </c>
       <c r="C93" t="n">
         <v>28.89500045776367</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>22.83426475524902</v>
+        <v>22.83425712585449</v>
       </c>
       <c r="C94" t="n">
         <v>30.9950008392334</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>23.93563461303711</v>
+        <v>23.93563270568848</v>
       </c>
       <c r="C95" t="n">
         <v>32.4900016784668</v>
@@ -2722,7 +2722,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>24.58242988586426</v>
+        <v>24.58243942260742</v>
       </c>
       <c r="C96" t="n">
         <v>33.18500137329102</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>24.74169540405273</v>
+        <v>24.74170112609863</v>
       </c>
       <c r="C97" t="n">
         <v>33.40000152587891</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>23.25275421142578</v>
+        <v>23.25275230407715</v>
       </c>
       <c r="C98" t="n">
         <v>31.38999938964844</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>23.87580108642578</v>
+        <v>23.87580490112305</v>
       </c>
       <c r="C99" t="n">
         <v>32.04000091552734</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>22.95208930969238</v>
+        <v>22.95208740234375</v>
       </c>
       <c r="C102" t="n">
         <v>30.61499977111816</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>23.33443260192871</v>
+        <v>23.33443450927734</v>
       </c>
       <c r="C103" t="n">
         <v>31.125</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>22.3935546875</v>
+        <v>22.39355659484863</v>
       </c>
       <c r="C104" t="n">
         <v>29.8700008392334</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>21.97028541564941</v>
+        <v>21.97028923034668</v>
       </c>
       <c r="C106" t="n">
         <v>29.125</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>22.52850914001465</v>
+        <v>22.52849578857422</v>
       </c>
       <c r="C107" t="n">
         <v>29.86499977111816</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>22.6776237487793</v>
+        <v>22.6776294708252</v>
       </c>
       <c r="C108" t="n">
         <v>29.86499977111816</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>23.19396781921387</v>
+        <v>23.19397735595703</v>
       </c>
       <c r="C109" t="n">
         <v>30.54500007629395</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>23.78440856933594</v>
+        <v>23.7844066619873</v>
       </c>
       <c r="C111" t="n">
         <v>31.125</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>24.45687484741211</v>
+        <v>24.45686531066895</v>
       </c>
       <c r="C112" t="n">
         <v>32.00500106811523</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>24.08625602722168</v>
+        <v>24.08625984191895</v>
       </c>
       <c r="C113" t="n">
         <v>31.52000045776367</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>23.91177558898926</v>
+        <v>23.91177177429199</v>
       </c>
       <c r="C115" t="n">
         <v>31.10000038146973</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>24.62297821044922</v>
+        <v>24.62297248840332</v>
       </c>
       <c r="C116" t="n">
         <v>32.02500152587891</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>22.66429710388184</v>
+        <v>22.66429901123047</v>
       </c>
       <c r="C117" t="n">
         <v>29.29999923706055</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>22.48252487182617</v>
+        <v>22.48252296447754</v>
       </c>
       <c r="C118" t="n">
         <v>29.06500053405762</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>24.6561279296875</v>
+        <v>24.65613174438477</v>
       </c>
       <c r="C119" t="n">
         <v>31.875</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>25.39712333679199</v>
+        <v>25.39711570739746</v>
       </c>
       <c r="C120" t="n">
         <v>32.61999893188477</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>23.31832122802734</v>
+        <v>23.31832313537598</v>
       </c>
       <c r="C121" t="n">
         <v>29.95000076293945</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>22.56310653686523</v>
+        <v>22.56310272216797</v>
       </c>
       <c r="C122" t="n">
         <v>28.97999954223633</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>23.33682060241699</v>
+        <v>23.33682250976562</v>
       </c>
       <c r="C123" t="n">
         <v>29.76000022888184</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>27.0420036315918</v>
+        <v>27.04201698303223</v>
       </c>
       <c r="C125" t="n">
         <v>34.48500061035156</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>27.39722633361816</v>
+        <v>27.39723205566406</v>
       </c>
       <c r="C126" t="n">
         <v>34.72999954223633</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>28.46220779418945</v>
+        <v>28.46220397949219</v>
       </c>
       <c r="C127" t="n">
         <v>36.08000183105469</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>28.50953674316406</v>
+        <v>28.50953483581543</v>
       </c>
       <c r="C128" t="n">
         <v>36.13999938964844</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>29.42449378967285</v>
+        <v>29.42449188232422</v>
       </c>
       <c r="C129" t="n">
         <v>37.09000015258789</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>28.50819969177246</v>
+        <v>28.50820541381836</v>
       </c>
       <c r="C130" t="n">
         <v>35.93500137329102</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>27.3182201385498</v>
+        <v>27.31821060180664</v>
       </c>
       <c r="C131" t="n">
         <v>34.43500137329102</v>
@@ -3766,7 +3766,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>28.48250770568848</v>
+        <v>28.48250961303711</v>
       </c>
       <c r="C132" t="n">
         <v>35.68999862670898</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>27.7722339630127</v>
+        <v>27.77223968505859</v>
       </c>
       <c r="C133" t="n">
         <v>34.79999923706055</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>29.04804992675781</v>
+        <v>29.04805374145508</v>
       </c>
       <c r="C135" t="n">
         <v>36.17499923706055</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>29.07615852355957</v>
+        <v>29.0761547088623</v>
       </c>
       <c r="C136" t="n">
         <v>36.20999908447266</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>30.4417724609375</v>
+        <v>30.44177436828613</v>
       </c>
       <c r="C138" t="n">
         <v>37.68999862670898</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>32.20658111572266</v>
+        <v>32.20657730102539</v>
       </c>
       <c r="C140" t="n">
         <v>39.875</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>33.51784896850586</v>
+        <v>33.51786422729492</v>
       </c>
       <c r="C141" t="n">
         <v>41.27500152587891</v>
@@ -4056,7 +4056,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>33.04686737060547</v>
+        <v>33.0468635559082</v>
       </c>
       <c r="C142" t="n">
         <v>40.69499969482422</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>34.06193161010742</v>
+        <v>34.06193923950195</v>
       </c>
       <c r="C143" t="n">
         <v>41.94499969482422</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>35.77530288696289</v>
+        <v>35.77531433105469</v>
       </c>
       <c r="C144" t="n">
         <v>43.81999969482422</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>35.83245086669922</v>
+        <v>35.83245468139648</v>
       </c>
       <c r="C145" t="n">
         <v>43.88999938964844</v>
@@ -4172,7 +4172,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>36.00389099121094</v>
+        <v>36.00389862060547</v>
       </c>
       <c r="C146" t="n">
         <v>44.09999847412109</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>36.49313735961914</v>
+        <v>36.49314117431641</v>
       </c>
       <c r="C147" t="n">
         <v>44.43999862670898</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>37.42108154296875</v>
+        <v>37.42108917236328</v>
       </c>
       <c r="C149" t="n">
         <v>45.56999969482422</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>37.21376800537109</v>
+        <v>37.21377182006836</v>
       </c>
       <c r="C150" t="n">
         <v>45.06000137329102</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>35.52899551391602</v>
+        <v>35.52899169921875</v>
       </c>
       <c r="C151" t="n">
         <v>43.02000045776367</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>38.43606185913086</v>
+        <v>38.43606567382812</v>
       </c>
       <c r="C152" t="n">
         <v>46.54000091552734</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>38.4017219543457</v>
+        <v>38.4017333984375</v>
       </c>
       <c r="C153" t="n">
         <v>46.2400016784668</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>39.09103393554688</v>
+        <v>39.09104156494141</v>
       </c>
       <c r="C154" t="n">
         <v>47.06999969482422</v>
@@ -4433,7 +4433,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>35.76908493041992</v>
+        <v>35.76908874511719</v>
       </c>
       <c r="C155" t="n">
         <v>43.06999969482422</v>
@@ -4462,7 +4462,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>38.20542526245117</v>
+        <v>38.20544052124023</v>
       </c>
       <c r="C156" t="n">
         <v>45.7400016784668</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>38.05509185791016</v>
+        <v>38.05508422851562</v>
       </c>
       <c r="C157" t="n">
         <v>45.56000137329102</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>39.84256744384766</v>
+        <v>39.84257125854492</v>
       </c>
       <c r="C158" t="n">
         <v>47.70000076293945</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>41.9937744140625</v>
+        <v>41.9937858581543</v>
       </c>
       <c r="C160" t="n">
         <v>50</v>
@@ -4607,7 +4607,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>42.31295013427734</v>
+        <v>42.31293106079102</v>
       </c>
       <c r="C161" t="n">
         <v>50.38000106811523</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>46.27310943603516</v>
+        <v>46.27310562133789</v>
       </c>
       <c r="C163" t="n">
         <v>54.81000137329102</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>44.44108963012695</v>
+        <v>44.44109344482422</v>
       </c>
       <c r="C164" t="n">
         <v>52.63999938964844</v>
@@ -4752,7 +4752,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>44.39849472045898</v>
+        <v>44.39849090576172</v>
       </c>
       <c r="C166" t="n">
         <v>52.31999969482422</v>
@@ -4810,7 +4810,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>46.76912307739258</v>
+        <v>46.76912689208984</v>
       </c>
       <c r="C168" t="n">
         <v>54.84000015258789</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>45.1146240234375</v>
+        <v>45.11463165283203</v>
       </c>
       <c r="C169" t="n">
         <v>52.90000152587891</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>43.98037719726562</v>
+        <v>43.98037338256836</v>
       </c>
       <c r="C170" t="n">
         <v>51.56999969482422</v>
@@ -4897,7 +4897,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>36.73849487304688</v>
+        <v>36.73849868774414</v>
       </c>
       <c r="C171" t="n">
         <v>42.84999847412109</v>
@@ -4926,7 +4926,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>29.35649871826172</v>
+        <v>29.35649681091309</v>
       </c>
       <c r="C172" t="n">
         <v>34.2400016784668</v>
@@ -4984,7 +4984,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>31.52243423461914</v>
+        <v>31.52244186401367</v>
       </c>
       <c r="C174" t="n">
         <v>36.47000122070312</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>31.14212799072266</v>
+        <v>31.14212226867676</v>
       </c>
       <c r="C175" t="n">
         <v>36.02999877929688</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>31.62920570373535</v>
+        <v>31.62920188903809</v>
       </c>
       <c r="C177" t="n">
         <v>36.31999969482422</v>
@@ -5100,7 +5100,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>31.65533065795898</v>
+        <v>31.65532875061035</v>
       </c>
       <c r="C178" t="n">
         <v>36.34999847412109</v>
@@ -5129,7 +5129,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>29.56529426574707</v>
+        <v>29.56529235839844</v>
       </c>
       <c r="C179" t="n">
         <v>33.95000076293945</v>
@@ -5158,7 +5158,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>38.50576019287109</v>
+        <v>38.50576400756836</v>
       </c>
       <c r="C180" t="n">
         <v>43.93000030517578</v>
@@ -5187,7 +5187,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>38.97909164428711</v>
+        <v>38.97908401489258</v>
       </c>
       <c r="C181" t="n">
         <v>44.47000122070312</v>
@@ -5216,7 +5216,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>39.60141754150391</v>
+        <v>39.60142135620117</v>
       </c>
       <c r="C182" t="n">
         <v>45.18000030517578</v>
@@ -5303,7 +5303,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>47.42928695678711</v>
+        <v>47.42929077148438</v>
       </c>
       <c r="C185" t="n">
         <v>53.72999954223633</v>
@@ -5332,7 +5332,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>50.32773208618164</v>
+        <v>50.32772445678711</v>
       </c>
       <c r="C186" t="n">
         <v>56.68000030517578</v>
@@ -5361,7 +5361,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>47.64617919921875</v>
+        <v>47.64618682861328</v>
       </c>
       <c r="C187" t="n">
         <v>53.65999984741211</v>
@@ -5390,7 +5390,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>48.83601379394531</v>
+        <v>48.83599853515625</v>
       </c>
       <c r="C188" t="n">
         <v>55</v>
@@ -5419,7 +5419,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>50.61812591552734</v>
+        <v>50.61812210083008</v>
       </c>
       <c r="C189" t="n">
         <v>56.68000030517578</v>
@@ -5448,7 +5448,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>46.55474853515625</v>
+        <v>46.55474090576172</v>
       </c>
       <c r="C190" t="n">
         <v>52.13000106811523</v>
@@ -5477,7 +5477,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>47.93004608154297</v>
+        <v>47.93003845214844</v>
       </c>
       <c r="C191" t="n">
         <v>53.66999816894531</v>
@@ -5535,7 +5535,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>52.44586944580078</v>
+        <v>52.44586563110352</v>
       </c>
       <c r="C193" t="n">
         <v>58.38999938964844</v>
@@ -5564,7 +5564,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>56.42488861083984</v>
+        <v>56.42490005493164</v>
       </c>
       <c r="C194" t="n">
         <v>62.81999969482422</v>
@@ -5622,7 +5622,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>58.19754791259766</v>
+        <v>58.19755172729492</v>
       </c>
       <c r="C196" t="n">
         <v>64.38999938964844</v>
@@ -5738,7 +5738,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>52.16072082519531</v>
+        <v>52.16072463989258</v>
       </c>
       <c r="C200" t="n">
         <v>57.29999923706055</v>
@@ -5825,7 +5825,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>59.65380096435547</v>
+        <v>59.6537971496582</v>
       </c>
       <c r="C203" t="n">
         <v>65.11000061035156</v>
@@ -5883,7 +5883,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>66.29740905761719</v>
+        <v>66.29741668701172</v>
       </c>
       <c r="C205" t="n">
         <v>71.94000244140625</v>
@@ -5912,7 +5912,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>67.73503875732422</v>
+        <v>67.73504638671875</v>
       </c>
       <c r="C206" t="n">
         <v>73.5</v>
@@ -5970,7 +5970,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>59.81317138671875</v>
+        <v>59.81316375732422</v>
       </c>
       <c r="C208" t="n">
         <v>64.51999664306641</v>
@@ -5999,7 +5999,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>64.75433349609375</v>
+        <v>64.75434112548828</v>
       </c>
       <c r="C209" t="n">
         <v>69.84999847412109</v>
@@ -6028,7 +6028,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>59.90649032592773</v>
+        <v>59.90649795532227</v>
       </c>
       <c r="C210" t="n">
         <v>64.20999908447266</v>
@@ -6086,7 +6086,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>67.49160766601562</v>
+        <v>67.49160003662109</v>
       </c>
       <c r="C212" t="n">
         <v>72.33999633789062</v>
@@ -6115,7 +6115,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>69.96682739257812</v>
+        <v>69.96683502197266</v>
       </c>
       <c r="C213" t="n">
         <v>74.56999969482422</v>
@@ -6231,7 +6231,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>77.80866241455078</v>
+        <v>77.80865478515625</v>
       </c>
       <c r="C217" t="n">
         <v>82.5</v>
@@ -6260,7 +6260,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>79.54401397705078</v>
+        <v>79.54402923583984</v>
       </c>
       <c r="C218" t="n">
         <v>84.33999633789062</v>
@@ -6289,7 +6289,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>76.63143157958984</v>
+        <v>76.63142395019531</v>
       </c>
       <c r="C219" t="n">
         <v>80.73999786376953</v>
@@ -6347,7 +6347,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>79.39334869384766</v>
+        <v>79.39335632324219</v>
       </c>
       <c r="C221" t="n">
         <v>83.65000152587891</v>
@@ -6405,7 +6405,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>85.25141906738281</v>
+        <v>85.25141143798828</v>
       </c>
       <c r="C223" t="n">
         <v>89.30999755859375</v>
@@ -6463,7 +6463,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>105.8498458862305</v>
+        <v>105.8498382568359</v>
       </c>
       <c r="C225" t="n">
         <v>110.3600006103516</v>
@@ -6492,7 +6492,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>107.2310028076172</v>
+        <v>107.2309951782227</v>
       </c>
       <c r="C226" t="n">
         <v>111.8000030517578</v>
@@ -6521,7 +6521,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>100.5074844360352</v>
+        <v>100.5074768066406</v>
       </c>
       <c r="C227" t="n">
         <v>104.7900009155273</v>
@@ -6550,7 +6550,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>109.8352508544922</v>
+        <v>109.8352661132812</v>
       </c>
       <c r="C228" t="n">
         <v>114</v>
@@ -6608,7 +6608,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>103.4571151733398</v>
+        <v>103.4570999145508</v>
       </c>
       <c r="C230" t="n">
         <v>107.379997253418</v>
@@ -6724,7 +6724,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>100.8693542480469</v>
+        <v>100.8693695068359</v>
       </c>
       <c r="C234" t="n">
         <v>103.5400009155273</v>
@@ -6753,7 +6753,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>102.7398376464844</v>
+        <v>102.7398452758789</v>
       </c>
       <c r="C235" t="n">
         <v>105.4599990844727</v>
@@ -6840,7 +6840,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>109.4125823974609</v>
+        <v>109.4125747680664</v>
       </c>
       <c r="C238" t="n">
         <v>111.6999969482422</v>
@@ -6869,7 +6869,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>104.9949340820312</v>
+        <v>104.9949417114258</v>
       </c>
       <c r="C239" t="n">
         <v>107.1900024414062</v>
